--- a/public/tool/app/http-soc-positioning-helper/template.xlsx
+++ b/public/tool/app/http-soc-positioning-helper/template.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,16 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -69,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -77,6 +87,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J200"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -458,256 +472,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>员工号</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>航班日期</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>出发地</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>目的地</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>航班号</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>申请原因</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>是否需要录入</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
   </sheetData>
   <autoFilter ref="A1:J200"/>
   <dataValidations count="2">
@@ -732,252 +547,252 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>申请原因</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>要客保障</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>商务跟机</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>保卫跟机</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>特殊装卸</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>军事信使</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>货机押运</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>本场训练</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>复训</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>体检</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>学习培训</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>调配飞行</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>调勤帮飞</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>执行航班</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>航班调整</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>模拟机</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>飞行改装</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>航线检查</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>安全监察</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>外籍休假</t>
         </is>
